--- a/data/availability/projects/m-squared-developments/trio.xlsx
+++ b/data/availability/projects/m-squared-developments/trio.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -859,7 +859,6 @@
       <c r="G2" t="n">
         <v>130</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -870,7 +869,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -916,7 +915,6 @@
       <c r="G3" t="n">
         <v>130</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -927,7 +925,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -973,7 +971,6 @@
       <c r="G4" t="n">
         <v>130</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -984,7 +981,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1030,7 +1027,6 @@
       <c r="G5" t="n">
         <v>130</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1041,7 +1037,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1087,7 +1083,6 @@
       <c r="G6" t="n">
         <v>130</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1098,7 +1093,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1144,7 +1139,6 @@
       <c r="G7" t="n">
         <v>130</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1155,7 +1149,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1201,7 +1195,6 @@
       <c r="G8" t="n">
         <v>255</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1212,7 +1205,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1258,7 +1251,6 @@
       <c r="G9" t="n">
         <v>290</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1269,7 +1261,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1315,7 +1307,6 @@
       <c r="G10" t="n">
         <v>145</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1372,7 +1363,6 @@
       <c r="G11" t="n">
         <v>135</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1429,7 +1419,6 @@
       <c r="G12" t="n">
         <v>135</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1486,7 +1475,6 @@
       <c r="G13" t="n">
         <v>150</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1543,7 +1531,6 @@
       <c r="G14" t="n">
         <v>241.7</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1554,7 +1541,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1600,7 +1587,6 @@
       <c r="G15" t="n">
         <v>241.7</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1611,7 +1597,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8/5/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
